--- a/tests/data/alphabet_vocab.xlsx
+++ b/tests/data/alphabet_vocab.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
   <si>
     <t xml:space="preserve">ConceptScheme</t>
   </si>
@@ -58,12 +58,21 @@
     <t xml:space="preserve">Narrower</t>
   </si>
   <si>
+    <t xml:space="preserve">RelatedScheme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Related</t>
   </si>
   <si>
+    <t xml:space="preserve">CloseMatchScheme</t>
+  </si>
+  <si>
     <t xml:space="preserve">CloseMatch</t>
   </si>
   <si>
+    <t xml:space="preserve">ExactMatchScheme</t>
+  </si>
+  <si>
     <t xml:space="preserve">ExactMatch</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
     <t xml:space="preserve">A house is a residential building typically split into different functional rooms. Houses can be built from a variety of materials and traditional houses will often reflect materials that are available locally.</t>
   </si>
   <si>
+    <t xml:space="preserve">Structure</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/House</t>
   </si>
   <si>
@@ -220,7 +232,7 @@
     <t xml:space="preserve">Octopus</t>
   </si>
   <si>
-    <t xml:space="preserve">An octopus is a soft-bodied, eight-limbed mollusc of the class Cephalopod. They live in the ocean and are known for their intelligence, and in some species ability to camoflage and expell ink when threatened.</t>
+    <t xml:space="preserve">An octopus is a soft-bodied, eight-limbed mollusc of the class Cephalopod. They live in the ocean and are known for their intelligence, and in some species have the ability to camoflage and expell ink when threatened.</t>
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Octopus</t>
@@ -369,7 +381,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,7 +391,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF5429"/>
+        <bgColor rgb="FFFF860D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF860D"/>
         <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD428"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -417,7 +441,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -436,6 +460,14 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -504,8 +536,8 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFFD428"/>
+      <rgbColor rgb="FFFF860D"/>
       <rgbColor rgb="FFFF5429"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -633,7 +665,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.86"/>
@@ -648,12 +680,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="30.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="30.88"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -690,692 +724,713 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>25</v>
+      <c r="S3" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>32</v>
+      <c r="S5" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>41</v>
+        <v>31</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>55</v>
+        <v>19</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>58</v>
+        <v>24</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>61</v>
+        <v>31</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>67</v>
+        <v>31</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P21" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P22" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="P24" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="P25" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P26" s="7" t="s">
-        <v>95</v>
+        <v>31</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>98</v>
+        <v>31</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="P2" r:id="rId1" display="https://en.wikipedia.org/wiki/Apple"/>
-    <hyperlink ref="P3" r:id="rId2" display="https://en.wikipedia.org/wiki/Banana"/>
-    <hyperlink ref="P4" r:id="rId3" display="https://en.wikipedia.org/wiki/Cat"/>
-    <hyperlink ref="P5" r:id="rId4" display="https://en.wikipedia.org/wiki/Dog"/>
-    <hyperlink ref="P6" r:id="rId5" display="https://en.wikipedia.org/wiki/Elephant"/>
-    <hyperlink ref="P7" r:id="rId6" display="https://en.wikipedia.org/wiki/Fox"/>
-    <hyperlink ref="P8" r:id="rId7" display="https://en.wikipedia.org/wiki/Goat"/>
-    <hyperlink ref="P9" r:id="rId8" display="https://en.wikipedia.org/wiki/House"/>
-    <hyperlink ref="P10" r:id="rId9" display="https://en.wikipedia.org/wiki/Imagination"/>
-    <hyperlink ref="P11" r:id="rId10" display="https://en.wikipedia.org/wiki/Jungle"/>
-    <hyperlink ref="P12" r:id="rId11" display="https://en.wikipedia.org/wiki/King"/>
-    <hyperlink ref="P13" r:id="rId12" display="https://en.wikipedia.org/wiki/Lemon"/>
-    <hyperlink ref="P14" r:id="rId13" display="https://en.wikipedia.org/wiki/Mouse"/>
-    <hyperlink ref="P15" r:id="rId14" display="https://en.wikipedia.org/wiki/Nest"/>
-    <hyperlink ref="P16" r:id="rId15" display="https://en.wikipedia.org/wiki/Octopus"/>
-    <hyperlink ref="P18" r:id="rId16" display="https://en.wikipedia.org/wiki/Queen_regnant"/>
-    <hyperlink ref="P19" r:id="rId17" display="https://en.wikipedia.org/wiki/Rain"/>
-    <hyperlink ref="P20" r:id="rId18" display="https://en.wikipedia.org/wiki/Sun"/>
-    <hyperlink ref="P21" r:id="rId19" display="https://en.wikipedia.org/wiki/Train"/>
-    <hyperlink ref="P22" r:id="rId20" display="https://en.wikipedia.org/wiki/Umbrella"/>
-    <hyperlink ref="P23" r:id="rId21" display="https://en.wikipedia.org/wiki/Village"/>
-    <hyperlink ref="P24" r:id="rId22" display="https://en.wikipedia.org/wiki/Wheel"/>
-    <hyperlink ref="P25" r:id="rId23" display="https://en.wikipedia.org/wiki/Xylophone"/>
-    <hyperlink ref="P26" r:id="rId24" display="https://en.wikipedia.org/wiki/Yak"/>
-    <hyperlink ref="P27" r:id="rId25" display="https://en.wikipedia.org/wiki/Zebra"/>
+    <hyperlink ref="S2" r:id="rId1" display="https://en.wikipedia.org/wiki/Apple"/>
+    <hyperlink ref="S3" r:id="rId2" display="https://en.wikipedia.org/wiki/Banana"/>
+    <hyperlink ref="S4" r:id="rId3" display="https://en.wikipedia.org/wiki/Cat"/>
+    <hyperlink ref="S5" r:id="rId4" display="https://en.wikipedia.org/wiki/Dog"/>
+    <hyperlink ref="S6" r:id="rId5" display="https://en.wikipedia.org/wiki/Elephant"/>
+    <hyperlink ref="S7" r:id="rId6" display="https://en.wikipedia.org/wiki/Fox"/>
+    <hyperlink ref="S8" r:id="rId7" display="https://en.wikipedia.org/wiki/Goat"/>
+    <hyperlink ref="S9" r:id="rId8" display="https://en.wikipedia.org/wiki/House"/>
+    <hyperlink ref="S10" r:id="rId9" display="https://en.wikipedia.org/wiki/Imagination"/>
+    <hyperlink ref="S11" r:id="rId10" display="https://en.wikipedia.org/wiki/Jungle"/>
+    <hyperlink ref="S12" r:id="rId11" display="https://en.wikipedia.org/wiki/King"/>
+    <hyperlink ref="S13" r:id="rId12" display="https://en.wikipedia.org/wiki/Lemon"/>
+    <hyperlink ref="S14" r:id="rId13" display="https://en.wikipedia.org/wiki/Mouse"/>
+    <hyperlink ref="S15" r:id="rId14" display="https://en.wikipedia.org/wiki/Nest"/>
+    <hyperlink ref="S16" r:id="rId15" display="https://en.wikipedia.org/wiki/Octopus"/>
+    <hyperlink ref="S18" r:id="rId16" display="https://en.wikipedia.org/wiki/Queen_regnant"/>
+    <hyperlink ref="S19" r:id="rId17" display="https://en.wikipedia.org/wiki/Rain"/>
+    <hyperlink ref="S20" r:id="rId18" display="https://en.wikipedia.org/wiki/Sun"/>
+    <hyperlink ref="S21" r:id="rId19" display="https://en.wikipedia.org/wiki/Train"/>
+    <hyperlink ref="S22" r:id="rId20" display="https://en.wikipedia.org/wiki/Umbrella"/>
+    <hyperlink ref="S23" r:id="rId21" display="https://en.wikipedia.org/wiki/Village"/>
+    <hyperlink ref="S24" r:id="rId22" display="https://en.wikipedia.org/wiki/Wheel"/>
+    <hyperlink ref="S25" r:id="rId23" display="https://en.wikipedia.org/wiki/Xylophone"/>
+    <hyperlink ref="S26" r:id="rId24" display="https://en.wikipedia.org/wiki/Yak"/>
+    <hyperlink ref="S27" r:id="rId25" display="https://en.wikipedia.org/wiki/Zebra"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/tests/data/alphabet_vocab.xlsx
+++ b/tests/data/alphabet_vocab.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="114">
   <si>
     <t xml:space="preserve">ConceptScheme</t>
   </si>
@@ -244,6 +244,9 @@
     <t xml:space="preserve">A parrot is a bird with a strong curved beak, upright stance and clawed feet. They are broadly classified into four familes and are found in the wild, and sometimes as pets. They are among the most intelligent of birds and typically eat seeds, nuts or fruit.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Parrot</t>
+  </si>
+  <si>
     <t xml:space="preserve">A queen is a female monarch, equivalent in rank, title and position to a King. She will reign over a realm known as a kingdom.</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t xml:space="preserve">A train typically describes a series of connected vehicles that run along a railway track. They can be used to transport people or freight. A train is typically pulled by a locomotive (engine) though some trains might have their propulsion distributed acrooss carriages and powered by an external power-source. </t>
   </si>
   <si>
+    <t xml:space="preserve">Artifact</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Train</t>
   </si>
   <si>
@@ -329,6 +335,33 @@
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Zebra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A multicellular, eukaryotic organism. Animals are different from other living things in that they cannot produce their own food, and tend to have to ingest organic material to survive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An object or thing created as the result of human craftmanship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An often edible component of a plant or vegetable that hosts seeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A leadership role assigned to a person who rules over a kingdom or realm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A physical arrangement of components that conforms to a template or pattern. Can be the result of natural or artificial processes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Structure</t>
   </si>
 </sst>
 </file>
@@ -338,7 +371,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -369,6 +402,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -441,7 +481,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -479,6 +519,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,7 +709,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.86"/>
@@ -1158,6 +1202,9 @@
       <c r="L17" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="S17" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -1176,7 +1223,7 @@
         <v>58</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>57</v>
@@ -1188,7 +1235,7 @@
         <v>55</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1202,16 +1249,16 @@
         <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1225,16 +1272,16 @@
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1248,16 +1295,19 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,16 +1321,19 @@
         <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="S22" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1294,16 +1347,16 @@
         <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1317,16 +1370,19 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1340,16 +1396,19 @@
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1363,19 +1422,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1389,19 +1448,131 @@
         <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="S28" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S30" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S31" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="S32" s="10" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1421,16 +1592,21 @@
     <hyperlink ref="S14" r:id="rId13" display="https://en.wikipedia.org/wiki/Mouse"/>
     <hyperlink ref="S15" r:id="rId14" display="https://en.wikipedia.org/wiki/Nest"/>
     <hyperlink ref="S16" r:id="rId15" display="https://en.wikipedia.org/wiki/Octopus"/>
-    <hyperlink ref="S18" r:id="rId16" display="https://en.wikipedia.org/wiki/Queen_regnant"/>
-    <hyperlink ref="S19" r:id="rId17" display="https://en.wikipedia.org/wiki/Rain"/>
-    <hyperlink ref="S20" r:id="rId18" display="https://en.wikipedia.org/wiki/Sun"/>
-    <hyperlink ref="S21" r:id="rId19" display="https://en.wikipedia.org/wiki/Train"/>
-    <hyperlink ref="S22" r:id="rId20" display="https://en.wikipedia.org/wiki/Umbrella"/>
-    <hyperlink ref="S23" r:id="rId21" display="https://en.wikipedia.org/wiki/Village"/>
-    <hyperlink ref="S24" r:id="rId22" display="https://en.wikipedia.org/wiki/Wheel"/>
-    <hyperlink ref="S25" r:id="rId23" display="https://en.wikipedia.org/wiki/Xylophone"/>
-    <hyperlink ref="S26" r:id="rId24" display="https://en.wikipedia.org/wiki/Yak"/>
-    <hyperlink ref="S27" r:id="rId25" display="https://en.wikipedia.org/wiki/Zebra"/>
+    <hyperlink ref="S17" r:id="rId16" display="https://en.wikipedia.org/wiki/Parrot"/>
+    <hyperlink ref="S18" r:id="rId17" display="https://en.wikipedia.org/wiki/Queen_regnant"/>
+    <hyperlink ref="S19" r:id="rId18" display="https://en.wikipedia.org/wiki/Rain"/>
+    <hyperlink ref="S20" r:id="rId19" display="https://en.wikipedia.org/wiki/Sun"/>
+    <hyperlink ref="S21" r:id="rId20" display="https://en.wikipedia.org/wiki/Train"/>
+    <hyperlink ref="S22" r:id="rId21" display="https://en.wikipedia.org/wiki/Umbrella"/>
+    <hyperlink ref="S23" r:id="rId22" display="https://en.wikipedia.org/wiki/Village"/>
+    <hyperlink ref="S24" r:id="rId23" display="https://en.wikipedia.org/wiki/Wheel"/>
+    <hyperlink ref="S25" r:id="rId24" display="https://en.wikipedia.org/wiki/Xylophone"/>
+    <hyperlink ref="S26" r:id="rId25" display="https://en.wikipedia.org/wiki/Yak"/>
+    <hyperlink ref="S27" r:id="rId26" display="https://en.wikipedia.org/wiki/Zebra"/>
+    <hyperlink ref="S28" r:id="rId27" display="https://en.wikipedia.org/wiki/Animal"/>
+    <hyperlink ref="S30" r:id="rId28" display="https://en.wikipedia.org/wiki/Fruit"/>
+    <hyperlink ref="S31" r:id="rId29" display="https://en.wikipedia.org/wiki/Monarch"/>
+    <hyperlink ref="S32" r:id="rId30" display="https://en.wikipedia.org/wiki/Structure"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/tests/data/alphabet_vocab.xlsx
+++ b/tests/data/alphabet_vocab.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="116">
   <si>
     <t xml:space="preserve">ConceptScheme</t>
   </si>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Banana</t>
   </si>
   <si>
-    <t xml:space="preserve">A banana is an elongated, edible fruit (botalically a berry) of herbaceous plants of the genus Musa.</t>
+    <t xml:space="preserve">A banana is an elongated, edible fruit (botanically a berry) of herbaceous plants of the genus Musa.</t>
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Banana</t>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test.TestAlphabetVocab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A duplicated definition which, if assigned to kgmeta:Description, ought to be identified as a validation error based on the max-count of definitions allowed for an individual named object. Does/should skos:definition (which this field is mapped to for the purposes of vocabulary mappings) replace kgmeta:Description in this case? There’s strong validation on the kgmeta-field, perhaps there should also be a similar constraint set for equivalent skos-predicates. We probably don’t want multiple definitions for the same term.</t>
   </si>
 </sst>
 </file>
@@ -371,7 +377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -402,13 +408,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -481,7 +480,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,10 +518,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -709,7 +704,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.86"/>
@@ -1202,7 +1197,7 @@
       <c r="L17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S17" s="10" t="s">
+      <c r="S17" s="9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1482,7 +1477,7 @@
       <c r="I28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="9" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1525,7 +1520,7 @@
       <c r="I30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="S30" s="10" t="s">
+      <c r="S30" s="9" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1548,7 +1543,7 @@
       <c r="I31" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="S31" s="10" t="s">
+      <c r="S31" s="9" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1571,8 +1566,28 @@
       <c r="I32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S32" s="10" t="s">
+      <c r="S32" s="9" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/tests/data/alphabet_vocab.xlsx
+++ b/tests/data/alphabet_vocab.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="118">
   <si>
     <t xml:space="preserve">ConceptScheme</t>
   </si>
@@ -163,67 +163,73 @@
     <t xml:space="preserve">A house is a residential building typically split into different functional rooms. Houses can be built from a variety of materials and traditional houses will often reflect materials that are available locally.</t>
   </si>
   <si>
+    <t xml:space="preserve">Structure, Artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagination is a creative cognitive process in which theories and ideas can be generated, simulated and mentally experienced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Imagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jungle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A jungle is a biome consisting of dense forest and tangled vegetation found in tropical climates that feature warm and humid conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Jungle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaiser,Konig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A King is a royal title given to a male monarch who rules over a nation. A realm or nation over which a monarch reigns is called a Kingdom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monarch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A lemon is the pointed oval yellow fruit of small evergreen trees of the genus Citrus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Lemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mouse is a small rodent of the genus Mus. Mice typically have pointed snouts, small rounded ears and a long scaly tail. They can be found in multiple environments across the world, including urban environments where they can be considered vermin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A nest is a structure constructed by an animal to hold its eggs or young. Nests are typically attributed to birds, but members of all classes of vertebrates and some invertebrates construct nests.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagination is a creative cognitive process in which theories and ideas can be generated, simulated and mentally experienced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/Imagination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jungle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A jungle is a biome consisting of dense forest and tangled vegetation found in tropical climates that feature warm and humid conditions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/Jungle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A King is a royal title given to a male monarch who rules over a nation. A realm or nation over which a monarch reigns is called a Kingdom.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monarch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A lemon is the pointed oval yellow fruit of small evergreen trees of the genus Citrus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/Lemon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mouse is a small rodent of the genus Mus. Mice typically have pointed snouts, small rounded ears and a long scaly tail. They can be found in multiple environments across the world, including urban environments where they can be considered vermin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/Mouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A nest is a structure constructed by an animal to hold its eggs or young. Nests are typically attributed to birds, but members of all classes of vertebrates and some invertebrates construct nests.</t>
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Nest</t>
@@ -1055,20 +1061,23 @@
       <c r="F12" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="I12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1082,19 +1091,19 @@
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1108,19 +1117,19 @@
         <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1134,19 +1143,19 @@
         <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1160,19 +1169,19 @@
         <v>21</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1186,19 +1195,19 @@
         <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1212,16 +1221,16 @@
         <v>21</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>19</v>
@@ -1230,7 +1239,7 @@
         <v>55</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1244,16 +1253,16 @@
         <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1267,16 +1276,16 @@
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1290,19 +1299,19 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1316,19 +1325,19 @@
         <v>21</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="S22" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1342,16 +1351,16 @@
         <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1365,19 +1374,19 @@
         <v>21</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1391,19 +1400,19 @@
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1417,19 +1426,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1443,19 +1452,19 @@
         <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1475,10 +1484,10 @@
         <v>31</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,13 +1501,13 @@
         <v>21</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,10 +1527,10 @@
         <v>24</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1535,16 +1544,16 @@
         <v>21</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1558,21 +1567,21 @@
         <v>21</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>20</v>
@@ -1587,7 +1596,7 @@
         <v>22</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
